--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,108 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129893844</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bellvikhällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>549696</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7121479</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Tåsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129893844</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129893844</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129893844</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129893844</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -910,7 +910,7 @@
         <v>129893844</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104023241</v>
+        <v>104023243</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549528.2406320468</v>
+        <v>549528</v>
       </c>
       <c r="R2" t="n">
-        <v>7121333.02340418</v>
+        <v>7121333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,50 +786,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104023243</v>
+        <v>129893844</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flaskmyran-Tåsjöberget, Ång</t>
+          <t>Bellvikhällan, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549528.2406320468</v>
+        <v>549696</v>
       </c>
       <c r="R3" t="n">
-        <v>7121333.02340418</v>
+        <v>7121479</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-07-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Mycket rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,26 +876,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893844</v>
+        <v>104023241</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -918,34 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bellvikhällan, Ång</t>
+          <t>Flaskmyran-Tåsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549696</v>
+        <v>549528</v>
       </c>
       <c r="R4" t="n">
-        <v>7121479</v>
+        <v>7121333</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,17 +953,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Mycket rikligt</t>
+          <t>2022-07-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,15 +983,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54637-2025 artfynd.xlsx
+++ b/artfynd/A 54637-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,8 +1011,18 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104023241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>